--- a/laporan_padel_dki_jakarta_2026-09-27.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-27.xlsx
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.240.000</t>
+          <t>Rp9.740.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>68</v>
       </c>
       <c r="D25" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp390.000</t>
+          <t>Rp195.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp4.833.000</t>
+          <t>Rp5.012.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>96</v>
       </c>
       <c r="D47" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp5.175.000</t>
+          <t>Rp5.252.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp894.000</t>
+          <t>Rp1.043.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>119</v>
       </c>
       <c r="D60" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp745.000</t>
+          <t>Rp447.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>96</v>
       </c>
       <c r="D74" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp8.075.000</t>
+          <t>Rp7.940.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>85</v>
       </c>
       <c r="D79" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp7.350.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>135</v>
       </c>
       <c r="D83" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.050.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp8.460.000</t>
+          <t>Rp8.955.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.460.000</t>
+          <t>Rp2.685.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4563,16 +4563,16 @@
         <v>75</v>
       </c>
       <c r="D36" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.990.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>77</v>
       </c>
       <c r="D46" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp9.500.000</t>
+          <t>Rp10.600.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>112</v>
       </c>
       <c r="D58" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.700.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp910.000</t>
+          <t>Rp999.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5338,16 +5338,16 @@
         <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.380.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.400.000</t>
+          <t>Rp15.785.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.950.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.109.000</t>
+          <t>Rp2.507.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp198.000</t>
+          <t>Rp297.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.570.000</t>
+          <t>Rp13.960.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.191.000</t>
+          <t>Rp1.489.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp28.900.000</t>
+          <t>Rp29.500.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>102</v>
       </c>
       <c r="D48" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.780.000</t>
+          <t>Rp15.970.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.255.000</t>
+          <t>Rp3.555.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp4.420.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.305.000</t>
+          <t>Rp1.450.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.240.000</t>
+          <t>Rp3.665.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp9.870.000</t>
+          <t>Rp9.450.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.599.977</t>
+          <t>Rp4.799.976</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp525.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.510.000</t>
+          <t>Rp3.915.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-27.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-27.xlsx
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.772.000</t>
+          <t>Rp3.168.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.968.000</t>
+          <t>Rp3.242.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.097.000</t>
+          <t>Rp3.322.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.740.000</t>
+          <t>Rp10.070.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp3.278.000</t>
+          <t>Rp2.980.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp15.721.000</t>
+          <t>Rp16.271.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp16.050.000</t>
+          <t>Rp16.835.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1350,16 +1350,16 @@
         <v>68</v>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp4.776.000</t>
+          <t>Rp4.974.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp3.346.000</t>
+          <t>Rp3.790.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>54</v>
       </c>
       <c r="D40" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp4.403.000</t>
+          <t>Rp4.502.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>60</v>
       </c>
       <c r="D44" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.653.000</t>
+          <t>Rp1.752.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>45</v>
       </c>
       <c r="D45" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.550.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>54</v>
       </c>
       <c r="D46" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp2.890.000</t>
+          <t>Rp3.090.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>96</v>
       </c>
       <c r="D47" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp5.252.000</t>
+          <t>Rp5.502.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp1.590.000</t>
+          <t>Rp1.980.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp4.896.000</t>
+          <t>Rp5.760.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp270.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.043.000</t>
+          <t>Rp1.341.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>48</v>
       </c>
       <c r="D56" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2218,16 +2218,16 @@
         <v>32</v>
       </c>
       <c r="D58" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp3.375.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>32</v>
       </c>
       <c r="D67" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>128</v>
       </c>
       <c r="D69" t="n">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp1.194.000</t>
+          <t>Rp2.239.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp2.215.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>120</v>
       </c>
       <c r="D76" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp8.405.000</t>
+          <t>Rp8.600.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>108</v>
       </c>
       <c r="D77" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp4.025.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2900,16 +2900,16 @@
         <v>54</v>
       </c>
       <c r="D80" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>96</v>
       </c>
       <c r="D84" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>30.2%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp9.750.000</t>
+          <t>Rp8.550.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp5.900.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.187.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.570.013</t>
+          <t>Rp18.746.013</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp8.558.000</t>
+          <t>Rp10.892.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp11.850.000</t>
+          <t>Rp12.150.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>90</v>
       </c>
       <c r="D6" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp4.030.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3912,16 +3912,16 @@
         <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp998.000</t>
+          <t>Rp1.198.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.160.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp250.000</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -4160,16 +4160,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.685.000</t>
+          <t>Rp3.135.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp1.430.000</t>
+          <t>Rp1.560.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>53</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp13.200.000</t>
+          <t>Rp12.600.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4408,16 +4408,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4439,16 +4439,16 @@
         <v>72</v>
       </c>
       <c r="D32" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.130.000</t>
+          <t>Rp2.380.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>176</v>
       </c>
       <c r="D38" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp10.000.000</t>
+          <t>Rp10.900.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>77</v>
       </c>
       <c r="D46" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp10.600.000</t>
+          <t>Rp11.250.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp7.900.000</t>
+          <t>Rp8.650.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5152,16 +5152,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>68</v>
       </c>
       <c r="D57" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp7.975.000</t>
+          <t>Rp8.635.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp999.000</t>
+          <t>Rp1.186.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>51</v>
       </c>
       <c r="D60" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp4.025.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5431,16 +5431,16 @@
         <v>36</v>
       </c>
       <c r="D64" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.785.000</t>
+          <t>Rp18.095.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp640.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp21.900.000</t>
+          <t>Rp22.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.950.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.507.000</t>
+          <t>Rp3.104.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6071,16 +6071,16 @@
         <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp335.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp720.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.420.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp4.986.000</t>
+          <t>Rp4.482.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.065.000</t>
+          <t>Rp12.290.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.825.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp15.830.000</t>
+          <t>Rp16.000.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.925.000</t>
+          <t>Rp7.225.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp3.506.000</t>
+          <t>Rp4.274.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.489.000</t>
+          <t>Rp1.787.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.450.000</t>
+          <t>Rp18.050.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7021,16 +7021,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.966.000</t>
+          <t>Rp7.371.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp1.755.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp13.675.000</t>
+          <t>Rp15.675.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>108</v>
       </c>
       <c r="D35" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.788.000</t>
+          <t>Rp2.086.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>14</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp15.073.000</t>
+          <t>Rp15.671.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>128</v>
       </c>
       <c r="D40" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.196.000</t>
+          <t>Rp1.794.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp29.500.000</t>
+          <t>Rp30.100.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.555.000</t>
+          <t>Rp3.855.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.310.000</t>
+          <t>Rp3.320.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.420.000</t>
+          <t>Rp4.760.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.795.500</t>
+          <t>Rp8.695.500</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.999.985</t>
+          <t>Rp3.399.983</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.665.000</t>
+          <t>Rp4.615.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp11.200.000</t>
+          <t>Rp11.600.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp9.450.000</t>
+          <t>Rp9.870.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp219.000</t>
+          <t>Rp100.000 - Rp219.000</t>
         </is>
       </c>
     </row>
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.799.976</t>
+          <t>Rp5.399.973</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.850.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.430.000</t>
+          <t>Rp3.410.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.050.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.085.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp6.590.000</t>
+          <t>Rp7.290.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.220.000</t>
+          <t>Rp2.960.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.915.000</t>
+          <t>Rp4.320.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp8.900.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-27.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-27.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.410.000</t>
+          <t>Rp2.620.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.150.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.168.000</t>
+          <t>Rp3.960.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>64</v>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.672.000</t>
+          <t>Rp2.112.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.070.000</t>
+          <t>Rp10.570.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.271.000</t>
+          <t>Rp16.683.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp3.780.000</t>
+          <t>Rp3.920.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp16.835.000</t>
+          <t>Rp17.840.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>64</v>
       </c>
       <c r="D24" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.025.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp447.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>64</v>
       </c>
       <c r="D31" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.490.000</t>
+          <t>Rp3.070.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.120.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>72</v>
       </c>
       <c r="D36" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.730.000</t>
+          <t>Rp5.350.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>64</v>
       </c>
       <c r="D37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp5.012.000</t>
+          <t>Rp5.370.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>32</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>72</v>
       </c>
       <c r="D39" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>51</v>
       </c>
       <c r="D41" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.350.000</t>
+          <t>Rp1.620.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>180</v>
       </c>
       <c r="D42" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.900.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>60</v>
       </c>
       <c r="D44" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.752.000</t>
+          <t>Rp2.152.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>96</v>
       </c>
       <c r="D47" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp5.502.000</t>
+          <t>Rp5.579.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2001,16 +2001,16 @@
         <v>64</v>
       </c>
       <c r="D51" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.760.000</t>
+          <t>Rp7.776.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>28</v>
       </c>
       <c r="D52" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp990.000</t>
+          <t>Rp1.188.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>17</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp1.341.000</t>
+          <t>Rp1.490.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>36</v>
       </c>
       <c r="D59" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp298.000</t>
+          <t>Rp447.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>90</v>
       </c>
       <c r="D61" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp1.054.000</t>
+          <t>Rp2.326.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>72</v>
       </c>
       <c r="D62" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.530.000</t>
+          <t>Rp2.390.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2466,16 +2466,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp3.844.000</t>
+          <t>Rp4.342.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>128</v>
       </c>
       <c r="D69" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.239.000</t>
+          <t>Rp2.936.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>96</v>
       </c>
       <c r="D70" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.139.000</t>
+          <t>Rp4.734.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2652,16 +2652,16 @@
         <v>72</v>
       </c>
       <c r="D72" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp1.725.000</t>
+          <t>Rp2.120.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>112</v>
       </c>
       <c r="D75" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp1.760.000</t>
+          <t>Rp2.075.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>85</v>
       </c>
       <c r="D79" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>36</v>
       </c>
       <c r="D81" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp250.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>96</v>
       </c>
       <c r="D84" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>30.2%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp8.550.000</t>
+          <t>Rp7.350.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3055,16 +3055,16 @@
         <v>36</v>
       </c>
       <c r="D85" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp4.460.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>138</v>
       </c>
       <c r="D87" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3148,16 +3148,16 @@
         <v>90</v>
       </c>
       <c r="D88" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>28</v>
       </c>
       <c r="D91" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp693.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>64</v>
       </c>
       <c r="D94" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp4.145.000</t>
+          <t>Rp4.365.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>112</v>
       </c>
       <c r="D95" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp5.900.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.746.013</t>
+          <t>Rp19.098.013</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.892.000</t>
+          <t>Rp12.448.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>32</v>
       </c>
       <c r="D11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.000.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>105</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp22.300.000</t>
+          <t>Rp23.650.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp5.083.000</t>
+          <t>Rp5.980.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>180</v>
       </c>
       <c r="D29" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp23.430.000</t>
+          <t>Rp23.980.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.250.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4625,16 +4625,16 @@
         <v>176</v>
       </c>
       <c r="D38" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp10.900.000</t>
+          <t>Rp11.350.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>64</v>
       </c>
       <c r="D45" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>32</v>
       </c>
       <c r="D50" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp664.000</t>
+          <t>Rp1.992.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>84</v>
       </c>
       <c r="D52" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp9.850.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp2.388.000</t>
+          <t>Rp2.985.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.186.000</t>
+          <t>Rp1.617.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.095.000</t>
+          <t>Rp21.560.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp22.400.000</t>
+          <t>Rp24.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.104.000</t>
+          <t>Rp3.701.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6102,16 +6102,16 @@
         <v>16</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.200.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp376.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp10.700.000</t>
+          <t>Rp10.880.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp297.000</t>
+          <t>Rp366.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp13.960.000</t>
+          <t>Rp14.350.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>102</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.720.000</t>
+          <t>Rp7.220.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.128.000</t>
+          <t>Rp2.256.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.274.000</t>
+          <t>Rp4.538.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.787.000</t>
+          <t>Rp2.085.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6959,16 +6959,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp891.000</t>
+          <t>Rp990.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.050.000</t>
+          <t>Rp19.450.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp7.371.000</t>
+          <t>Rp7.614.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.786.000</t>
+          <t>Rp2.985.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7238,16 +7238,16 @@
         <v>60</v>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp4.860.000</t>
+          <t>Rp6.780.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>80</v>
       </c>
       <c r="D30" t="n">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.975.000</t>
+          <t>Rp1.225.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7300,16 +7300,16 @@
         <v>72</v>
       </c>
       <c r="D31" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp15.675.000</t>
+          <t>Rp15.975.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>108</v>
       </c>
       <c r="D35" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp2.086.000</t>
+          <t>Rp2.384.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp15.671.000</t>
+          <t>Rp16.320.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>128</v>
       </c>
       <c r="D40" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.794.000</t>
+          <t>Rp2.093.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp10.375.000</t>
+          <t>Rp10.550.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp4.950.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>36</v>
       </c>
       <c r="D46" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp6.070.000</t>
+          <t>Rp5.270.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>102</v>
       </c>
       <c r="D48" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.450.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp3.575.000</t>
+          <t>Rp4.100.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>48</v>
       </c>
       <c r="D50" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.970.000</t>
+          <t>Rp16.730.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp920.000</t>
+          <t>Rp1.180.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8095,16 +8095,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.887.000</t>
+          <t>Rp4.485.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.855.000</t>
+          <t>Rp4.955.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.270.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp4.760.000</t>
+          <t>Rp6.120.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp8.695.500</t>
+          <t>Rp9.925.500</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.399.983</t>
+          <t>Rp3.599.982</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.450.000</t>
+          <t>Rp1.595.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.090.000</t>
+          <t>Rp2.470.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp11.600.000</t>
+          <t>Rp12.300.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp625.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp675.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp9.870.000</t>
+          <t>Rp10.920.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8698,7 +8698,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp219.000</t>
+          <t>Rp100.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.399.973</t>
+          <t>Rp6.399.968</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.625.000</t>
+          <t>Rp2.975.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.410.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8932,16 +8932,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp4.755.000</t>
+          <t>Rp5.415.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp2.960.000</t>
+          <t>Rp3.515.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.320.000</t>
+          <t>Rp5.265.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp8.900.000</t>
+          <t>Rp8.400.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>19.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.791.000</t>
+          <t>Rp2.587.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-27.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-27.xlsx
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2807,16 +2807,16 @@
         <v>108</v>
       </c>
       <c r="D77" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp4.175.000</t>
+          <t>Rp4.475.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>85</v>
       </c>
       <c r="D79" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp8.250.000</t>
+          <t>Rp8.550.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>80</v>
       </c>
       <c r="D86" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp10.852.000</t>
+          <t>Rp10.952.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.187.000</t>
+          <t>Rp2.268.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.000.000</t>
+          <t>Rp7.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp366.000</t>
+          <t>Rp504.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp14.350.000</t>
+          <t>Rp14.740.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.538.000</t>
+          <t>Rp4.714.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp15.975.000</t>
+          <t>Rp16.125.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>90</v>
       </c>
       <c r="D36" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>112</v>
       </c>
       <c r="D43" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp10.550.000</t>
+          <t>Rp10.775.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>102</v>
       </c>
       <c r="D48" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp3.450.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.120.000</t>
+          <t>Rp6.290.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp8.400.000</t>
+          <t>Rp8.550.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-27.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-27.xlsx
@@ -3633,16 +3633,16 @@
         <v>90</v>
       </c>
       <c r="D6" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp504.000</t>
+          <t>Rp772.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
